--- a/naver-place-crawler/results_nail/수원_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/수원_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V289"/>
+  <dimension ref="A1:V336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -27140,6 +27140,4244 @@
         </is>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>미희네일</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>031-269-1479</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>경기도 수원시 장안구 만석로19번길 11-7 대일프라자 7층 703호 미희네일</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/mihee_nail_</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P290" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>1</v>
+      </c>
+      <c r="R290" t="n">
+        <v>89</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>1120462399</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1120462399</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>누크네일</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>0507-1305-7651</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 도청로 95 1층 1-221호</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nooknail__?igsh=MXBiaTAycjgzMHlnNg%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P291" t="n">
+        <v>123</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>18</v>
+      </c>
+      <c r="R291" t="n">
+        <v>141</v>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>1137791832</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1137791832</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>하늘봄네일 오로지푸스 권선점</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>0507-1313-2982</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>경기도 수원시 권선구 권선로 708-9 202호</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/skyspringnail7/</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P292" t="n">
+        <v>805</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>17</v>
+      </c>
+      <c r="R292" t="n">
+        <v>822</v>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>1845156651</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1845156651</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>마리네일</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>0507-1392-8507</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>경기도 수원시 권선구 금곡로196번길 67 세광프라자 3층 옳음에스테틱 내 마리네일</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mari_nail_luv?igsh=MXdsYnZjNzluZHR5Yg%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P293" t="n">
+        <v>281</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>18</v>
+      </c>
+      <c r="R293" t="n">
+        <v>299</v>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>1732799481</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1732799481</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>네일은예지</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>0507-1485-1125</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>경기도 수원시 팔달구 효원로 278 파비오더씨타</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/naileunyeji</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P294" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>20</v>
+      </c>
+      <c r="R294" t="n">
+        <v>124</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>2080339175</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2080339175</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>블랑네일</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>ady0424@naver.com</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>0507-1306-8897</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>경기도 수원시 팔달구 권광로 181 씨네파크 4층 409호 블랑네일</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ady0424</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P295" t="n">
+        <v>496</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>756</v>
+      </c>
+      <c r="R295" t="n">
+        <v>1252</v>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>1946787286</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1946787286</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>코코네일</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>0507-1383-0402</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>경기도 수원시 권선구 동수원로46번길 23 1층 102호</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coco_nail2</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P296" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>11</v>
+      </c>
+      <c r="R296" t="n">
+        <v>98</v>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>1104707793</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1104707793</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>네일채</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>0507-1481-2430</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>경기도 수원시 장안구 율전로 107 1층 102호</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_BJvxdn</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P297" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q297" t="n">
+        <v>5</v>
+      </c>
+      <c r="R297" t="n">
+        <v>145</v>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>1992168024</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1992168024</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>네일두잉</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>0507-1427-5646</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 태장로36번길 36 근린생활시설동 210호</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>https://NAIL_DOING.homebuilder.co.kr</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P298" t="n">
+        <v>222</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>4</v>
+      </c>
+      <c r="R298" t="n">
+        <v>226</v>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>2084759671</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2084759671</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>꼼쟁이네퍼스널컬러네일</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>0507-1344-7662</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>경기도 수원시 장안구 화산로125번길 5 2층 204호</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kkom_nails</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P299" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>13</v>
+      </c>
+      <c r="R299" t="n">
+        <v>129</v>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>1055071397</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1055071397</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>라브로우 네일</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 도청로18번길 26 힐스테이트 광교중앙역 2층 248호</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P300" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>49</v>
+      </c>
+      <c r="R300" t="n">
+        <v>110</v>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>1200590491</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1200590491</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>쥬네일</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>0507-1457-1656</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>경기도 수원시 팔달구 향교로 27-1 202호</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_Xkxkxkn</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P301" t="n">
+        <v>171</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>21</v>
+      </c>
+      <c r="R301" t="n">
+        <v>192</v>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>2032396713</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2032396713</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>메리미네일</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr"/>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>031-213-0261</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 동수원로 448 매탄현대아파트 상가 1층</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/melimi_nail</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P302" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>8</v>
+      </c>
+      <c r="R302" t="n">
+        <v>26</v>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>1079802485</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1079802485</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>로미네일</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr"/>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>0507-1432-1670</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>경기도 수원시 팔달구 고등로 28 2층 203호</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P303" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>0</v>
+      </c>
+      <c r="R303" t="n">
+        <v>7</v>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>2080640829</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2080640829</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>닥터아이티엔 김원장네</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>taeilang@naver.com</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>0507-1431-8039</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>경기도 수원시 장안구 조원로24번길 17 1층</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/taeilang</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P304" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>21</v>
+      </c>
+      <c r="R304" t="n">
+        <v>30</v>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>1411791359</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1411791359</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>88뷰티</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr"/>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>0507-1383-2566</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>경기도 수원시 권선구 경수대로384번길 13 1층 102호</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/88beauty_nail?igshid=MTIzZWQxMDU=</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P305" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>38</v>
+      </c>
+      <c r="R305" t="n">
+        <v>125</v>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>1724991222</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1724991222</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>레푸스 화서역점 풋케어 발톱 발각질 문제성 발관리전문점</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>msso2015@naver.com</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>0507-1367-6896</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>경기도 수원시 팔달구 덕영대로 693 풍성프라자 602호</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_laxhIb/chat</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P306" t="n">
+        <v>284</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>208</v>
+      </c>
+      <c r="R306" t="n">
+        <v>492</v>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>1069943820</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1069943820</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>네일엔젤</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>031-235-3540</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>경기도 수원시 권선구 동수원로242번길 19 101호</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P307" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>1</v>
+      </c>
+      <c r="R307" t="n">
+        <v>51</v>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>34139164</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34139164</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>내성발톱무좀 풋풋하다</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>blessbeauty7@naver.com</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>0507-1378-3772</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 도청로18번길 26 3층 378호</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/footfoothd</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P308" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>167</v>
+      </c>
+      <c r="R308" t="n">
+        <v>417</v>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>1970948674</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1970948674</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>유니네일</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>0507-1364-6226</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 봉영로 1612 1층 130호</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yuni.nail_s2/</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P309" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>13</v>
+      </c>
+      <c r="R309" t="n">
+        <v>96</v>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>1460745490</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1460745490</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>네일포엣</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>0507-1389-2215</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>경기도 수원시 팔달구 권광로 184 캐슬타워 3층 323호 올라래쉬</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_poet</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P310" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>41</v>
+      </c>
+      <c r="R310" t="n">
+        <v>160</v>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>2018802554</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2018802554</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>라라네일</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>경기도 수원시 권선구 서수원로577번길 305 2단지상가 107호 라라네일</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P311" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>12</v>
+      </c>
+      <c r="R311" t="n">
+        <v>59</v>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>1476397479</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1476397479</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>도담네일</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>031-225-8844</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>경기도 수원시 권선구 동수원로177번길 40</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dodam__nail/</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P312" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>0</v>
+      </c>
+      <c r="R312" t="n">
+        <v>12</v>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>1599172735</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1599172735</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>루에르네일</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>0507-1466-0751</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>경기도 수원시 팔달구 효원로 278 2층 210호</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_lueur_nail</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P313" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>69</v>
+      </c>
+      <c r="R313" t="n">
+        <v>181</v>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>2005992433</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2005992433</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>뽐네일</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>0507-1401-3104</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>경기도 수원시 팔달구 중부대로223번길 20-7 1층 뽐네일</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bbom_nailumandong</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P314" t="n">
+        <v>192</v>
+      </c>
+      <c r="Q314" t="n">
+        <v>5</v>
+      </c>
+      <c r="R314" t="n">
+        <v>197</v>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>1213978595</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213978595</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>미앤모</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>0507-1348-4612</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>경기도 수원시 팔달구 고화로 37</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/minmo.nail</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr"/>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P315" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>1</v>
+      </c>
+      <c r="R315" t="n">
+        <v>1</v>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>1541706785</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1541706785</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>키스네일</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>0507-1368-9802</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>경기도 수원시 팔달구 갓매산로 43 은성빌딩 1층</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kissnail_suwon/</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P316" t="n">
+        <v>1208</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>834</v>
+      </c>
+      <c r="R316" t="n">
+        <v>2042</v>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>20955554</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20955554</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>엔더블유 네일왁싱</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>0507-1341-5437</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 반달로35번길 30 228호</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_fGZqs</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P317" t="n">
+        <v>1049</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>609</v>
+      </c>
+      <c r="R317" t="n">
+        <v>1658</v>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>1454353978</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1454353978</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>미스네일</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr"/>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>0507-1488-0137</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>경기도 수원시 권선구 구운중로22번길 2 1층 미스네일</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P318" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>2</v>
+      </c>
+      <c r="R318" t="n">
+        <v>7</v>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>1025657304</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1025657304</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>비비드네일 인계점</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>0507-1378-7444</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>경기도 수원시 권선구 효원로256번길 33 한라비발디파크 1층 비비드네일 인계점</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vividnail_mj</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P319" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>77</v>
+      </c>
+      <c r="R319" t="n">
+        <v>315</v>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>1624667760</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1624667760</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>봉담네일</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>0507-1319-6201</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>경기도 화성시 효행구 봉담읍 동화길 51 프리미엄원희캐슬201호(메종드j헤어샵 내)</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P320" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>3</v>
+      </c>
+      <c r="R320" t="n">
+        <v>194</v>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>1829560239</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1829560239</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>버던트네일</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr"/>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr"/>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 반달로35번길 30 3층 313호</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/verdant_nail?igsh=dGdrcmcxZXA5djA0&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P321" t="n">
+        <v>373</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>9</v>
+      </c>
+      <c r="R321" t="n">
+        <v>382</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>2082347591</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2082347591</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>네일, 고이</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>0507-1332-8241</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 태장로 81 4층 402-1호</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_goi</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P322" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>14</v>
+      </c>
+      <c r="R322" t="n">
+        <v>152</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>1483281136</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1483281136</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>뷰티혜네일</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>0507-1425-4767</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>경기도 수원시 장안구 율전로80번길 1-1 2층 202호</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_jmGxkG</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P323" t="n">
+        <v>516</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>102</v>
+      </c>
+      <c r="R323" t="n">
+        <v>618</v>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>1011425576</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1011425576</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>3.14네일</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>0507-1326-3140</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 도청로18번길 26 1층 174호</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/3.14nail</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P324" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>17</v>
+      </c>
+      <c r="R324" t="n">
+        <v>17</v>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>1950555068</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1950555068</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>난나네일</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>nanna_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>0507-1346-8290</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>경기도 수원시 장안구 하률로12번길 86 골든프라자 1층 NanNa,네일</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nanna_nail</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P325" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>4</v>
+      </c>
+      <c r="R325" t="n">
+        <v>119</v>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>1262106405</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1262106405</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>네일앤코</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>070-5100-0616</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 센트럴파크로127번길 131-3 1층 101호</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail._.ko?igsh=OGwweW53NnNtNnl6&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P326" t="n">
+        <v>327</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>6</v>
+      </c>
+      <c r="R326" t="n">
+        <v>333</v>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>1872894083</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1872894083</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>도나네일</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>0507-1332-8307</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>경기도 수원시 장안구 천천로21번길 33</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/DOHNANAIL</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P327" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>4</v>
+      </c>
+      <c r="R327" t="n">
+        <v>16</v>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>1211883516</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1211883516</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>네일주</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>경기도 수원시 장안구 조원로112번길 13 1층</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_ju2</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P328" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>3</v>
+      </c>
+      <c r="R328" t="n">
+        <v>119</v>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>1082600080</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1082600080</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>모몽네일</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>0507-1369-9166</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>경기도 수원시 장안구 정조로1051번길 47 1층 모몽네일</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/suwonmomong_nail</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P329" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>9</v>
+      </c>
+      <c r="R329" t="n">
+        <v>196</v>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>1059431415</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1059431415</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>제제네일 수원정자점</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>xx04@naver.com</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>0507-1447-7725</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>경기도 수원시 장안구 대평로90번길 19 라이프스포츠상가 1층 상가 안 제제네일</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>https://zero.gongbiz.kr/shop/S000015089</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P330" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>1</v>
+      </c>
+      <c r="R330" t="n">
+        <v>114</v>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>1255601255</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1255601255</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Gel Lee</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>070-9924-9854</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 봉영로 1590 밀레니엄프라자 507호</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P331" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>0</v>
+      </c>
+      <c r="R331" t="n">
+        <v>8</v>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>31591906</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31591906</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>헤이네일</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>0507-1441-4179</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>경기도 수원시 팔달구 팔달로99번길 56 2층 헤이네일</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_gLaxms</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P332" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>16</v>
+      </c>
+      <c r="R332" t="n">
+        <v>22</v>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>1257147862</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1257147862</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>릴네일 호매실점</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>0507-1322-8725</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>경기도 수원시 권선구 호매실로90번길 77 4층 409호</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_wAFxhX</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P333" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>1</v>
+      </c>
+      <c r="R333" t="n">
+        <v>14</v>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>2073697742</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2073697742</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>와이엘네일 광교점</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>0507-1319-9459</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>경기도 수원시 영통구 광교호수공원로 277 B2 100호 와이엘네일</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ylnail_</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P334" t="n">
+        <v>263</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>200</v>
+      </c>
+      <c r="R334" t="n">
+        <v>463</v>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>1838855809</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1838855809</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>유니뜨네일</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>0507-1407-4144</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>경기도 화성시 효행구 봉담읍 상리중심상가길 28-18 302호</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P335" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>17</v>
+      </c>
+      <c r="R335" t="n">
+        <v>184</v>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>1062054278</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1062054278</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>유유네일</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>0507-1400-1553</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>경기도 수원시 팔달구 효원로 278 파비오더씨타 1층 150호</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_Kqxkxfn</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P336" t="n">
+        <v>329</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>5</v>
+      </c>
+      <c r="R336" t="n">
+        <v>334</v>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>1708869492</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1708869492</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
